--- a/data/trans_orig/P1427-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1427-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cataratas en 2012</t>
+          <t>Población con diagnóstico de cataratas en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36590</t>
+          <t>36062</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>66610</t>
+          <t>64854</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>63957</t>
+          <t>66404</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>100892</t>
+          <t>102955</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>110006</t>
+          <t>110971</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>155858</t>
+          <t>157281</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>908033</t>
+          <t>909789</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>938053</t>
+          <t>938581</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1236905</t>
+          <t>1234842</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1273840</t>
+          <t>1271393</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2156582</t>
+          <t>2155159</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2202434</t>
+          <t>2201469</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8745</t>
+          <t>8492</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27551</t>
+          <t>26593</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3868</t>
+          <t>3829</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19087</t>
+          <t>20701</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16628</t>
+          <t>16086</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38327</t>
+          <t>39158</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1936406</t>
+          <t>1937364</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1955212</t>
+          <t>1955465</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1735505</t>
+          <t>1733891</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1750724</t>
+          <t>1750763</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3680222</t>
+          <t>3679391</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3701921</t>
+          <t>3702463</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>917</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7516</t>
+          <t>8430</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6634</t>
+          <t>6998</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>1871</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11315</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>473665</t>
+          <t>472751</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>480283</t>
+          <t>480264</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>451997</t>
+          <t>451633</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>928498</t>
+          <t>928183</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>937944</t>
+          <t>937942</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53197</t>
+          <t>52997</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>86979</t>
+          <t>87686</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75897</t>
+          <t>76146</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>114869</t>
+          <t>115294</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>138106</t>
+          <t>137805</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>191157</t>
+          <t>187707</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3332803</t>
+          <t>3332096</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3366585</t>
+          <t>3366785</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3436151</t>
+          <t>3435726</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3475123</t>
+          <t>3474874</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6779644</t>
+          <t>6783094</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6832695</t>
+          <t>6832996</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2140,7 +2140,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cataratas en 2016</t>
+          <t>Población con diagnóstico de cataratas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13037</t>
+          <t>12582</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29322</t>
+          <t>28939</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40842</t>
+          <t>41781</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>72129</t>
+          <t>73554</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60574</t>
+          <t>58881</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>94320</t>
+          <t>93372</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>725025</t>
+          <t>725408</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>741310</t>
+          <t>741765</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>922531</t>
+          <t>921106</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>953818</t>
+          <t>952879</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1654687</t>
+          <t>1655635</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1688433</t>
+          <t>1690126</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,63%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6449</t>
+          <t>6315</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19941</t>
+          <t>19899</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11088</t>
+          <t>10890</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28534</t>
+          <t>29409</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22283</t>
+          <t>20381</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44776</t>
+          <t>42866</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2056444</t>
+          <t>2056486</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2069936</t>
+          <t>2070070</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1959766</t>
+          <t>1958891</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1977212</t>
+          <t>1977410</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4019909</t>
+          <t>4021819</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4042402</t>
+          <t>4044304</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>954</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9341</t>
+          <t>8656</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2140</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14936</t>
+          <t>13415</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4880</t>
+          <t>4901</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17860</t>
+          <t>18168</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>537545</t>
+          <t>538230</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>545900</t>
+          <t>545932</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>534204</t>
+          <t>535725</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>547000</t>
+          <t>547035</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1078167</t>
+          <t>1077859</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1091147</t>
+          <t>1091126</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26082</t>
+          <t>26354</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49393</t>
+          <t>49736</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63564</t>
+          <t>62912</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101875</t>
+          <t>99155</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>96275</t>
+          <t>95102</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>138896</t>
+          <t>140188</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3328225</t>
+          <t>3327882</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3351536</t>
+          <t>3351264</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3430225</t>
+          <t>3432945</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3468536</t>
+          <t>3469188</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6770822</t>
+          <t>6769530</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6813443</t>
+          <t>6814616</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cataratas en 2023</t>
+          <t>Población con diagnóstico de cataratas en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47076</t>
+          <t>47054</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>68742</t>
+          <t>69825</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>91771</t>
+          <t>92236</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>122803</t>
+          <t>124700</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>145617</t>
+          <t>145065</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>186726</t>
+          <t>184280</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>444335</t>
+          <t>443252</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>466001</t>
+          <t>466023</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>629932</t>
+          <t>628035</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>660964</t>
+          <t>660499</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1079086</t>
+          <t>1081532</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1120195</t>
+          <t>1120747</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,54%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24217</t>
+          <t>25633</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50954</t>
+          <t>50427</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26802</t>
+          <t>26349</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48893</t>
+          <t>48100</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57203</t>
+          <t>59883</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>92523</t>
+          <t>97473</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2237296</t>
+          <t>2237823</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2264033</t>
+          <t>2262617</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2187583</t>
+          <t>2188376</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2209674</t>
+          <t>2210127</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4432203</t>
+          <t>4427253</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4467523</t>
+          <t>4464843</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5954</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16903</t>
+          <t>16284</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8015</t>
+          <t>8213</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22849</t>
+          <t>22818</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16568</t>
+          <t>16344</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33750</t>
+          <t>33190</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -4737,12 +4737,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>629018</t>
+          <t>629637</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>639967</t>
+          <t>639958</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>636336</t>
+          <t>636367</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>651170</t>
+          <t>650972</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1271356</t>
+          <t>1271916</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1288538</t>
+          <t>1288762</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>83174</t>
+          <t>80658</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>126607</t>
+          <t>126433</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>126806</t>
+          <t>130615</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>180479</t>
+          <t>182851</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>225312</t>
+          <t>223484</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>296674</t>
+          <t>295663</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3320641</t>
+          <t>3320815</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3364074</t>
+          <t>3366590</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3467917</t>
+          <t>3465545</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3521590</t>
+          <t>3517781</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6798970</t>
+          <t>6799981</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6870332</t>
+          <t>6872160</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,85%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1427-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1427-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36062</t>
+          <t>35393</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64854</t>
+          <t>65393</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>66404</t>
+          <t>66210</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>102955</t>
+          <t>101499</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>110971</t>
+          <t>108544</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>157281</t>
+          <t>157898</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>909789</t>
+          <t>909250</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>938581</t>
+          <t>939250</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1234842</t>
+          <t>1236298</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1271393</t>
+          <t>1271587</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2155159</t>
+          <t>2154542</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2201469</t>
+          <t>2203896</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8492</t>
+          <t>8457</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26593</t>
+          <t>26112</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3829</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20701</t>
+          <t>21204</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16086</t>
+          <t>16057</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39158</t>
+          <t>40935</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1937364</t>
+          <t>1937845</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1955465</t>
+          <t>1955500</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1733891</t>
+          <t>1733388</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1750763</t>
+          <t>1750311</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3679391</t>
+          <t>3677614</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3702463</t>
+          <t>3702492</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>918</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8430</t>
+          <t>9434</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6998</t>
+          <t>6891</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1871</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>10697</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>472751</t>
+          <t>471747</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>480264</t>
+          <t>480263</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>451633</t>
+          <t>451740</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>928183</t>
+          <t>929116</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>937942</t>
+          <t>937913</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52997</t>
+          <t>52712</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>87686</t>
+          <t>88077</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>76146</t>
+          <t>77112</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>115294</t>
+          <t>115695</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>137805</t>
+          <t>136828</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>187707</t>
+          <t>188434</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3332096</t>
+          <t>3331705</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3366785</t>
+          <t>3367070</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3435726</t>
+          <t>3435325</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3474874</t>
+          <t>3473908</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6783094</t>
+          <t>6782367</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6832996</t>
+          <t>6833973</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12582</t>
+          <t>12563</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28939</t>
+          <t>30271</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41781</t>
+          <t>41810</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>73554</t>
+          <t>73165</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>58881</t>
+          <t>59741</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>93372</t>
+          <t>95236</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>725408</t>
+          <t>724076</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>741765</t>
+          <t>741784</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>921106</t>
+          <t>921495</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>952879</t>
+          <t>952850</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1655635</t>
+          <t>1653771</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1690126</t>
+          <t>1689266</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6315</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19899</t>
+          <t>21241</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10890</t>
+          <t>11063</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29409</t>
+          <t>29701</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20381</t>
+          <t>19990</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42866</t>
+          <t>43569</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2056486</t>
+          <t>2055144</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2070070</t>
+          <t>2070107</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1958891</t>
+          <t>1958599</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1977410</t>
+          <t>1977237</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4021819</t>
+          <t>4021116</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4044304</t>
+          <t>4044695</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>979</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8656</t>
+          <t>9632</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2141</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13415</t>
+          <t>14703</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4901</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18168</t>
+          <t>18975</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>538230</t>
+          <t>537254</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>545932</t>
+          <t>545907</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>535725</t>
+          <t>534437</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>547035</t>
+          <t>546999</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1077859</t>
+          <t>1077052</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1091126</t>
+          <t>1091244</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26354</t>
+          <t>26132</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49736</t>
+          <t>49195</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62912</t>
+          <t>63467</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>99155</t>
+          <t>99736</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>95102</t>
+          <t>96807</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>140188</t>
+          <t>139907</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3327882</t>
+          <t>3328423</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3351264</t>
+          <t>3351486</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3432945</t>
+          <t>3432364</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3469188</t>
+          <t>3468633</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6769530</t>
+          <t>6769811</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6814616</t>
+          <t>6812911</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -3933,32 +3933,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>57465</t>
+          <t>59048</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47054</t>
+          <t>47431</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69825</t>
+          <t>70787</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3968,32 +3968,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>106046</t>
+          <t>109408</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>92236</t>
+          <t>96466</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>124700</t>
+          <t>124316</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4003,32 +4003,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>163510</t>
+          <t>168456</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>145065</t>
+          <t>150201</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>184280</t>
+          <t>188164</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>13,46%</t>
         </is>
       </c>
     </row>
@@ -4046,32 +4046,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>455612</t>
+          <t>517553</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>443252</t>
+          <t>505814</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>466023</t>
+          <t>529170</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4081,32 +4081,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>646689</t>
+          <t>711449</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>628035</t>
+          <t>696541</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>660499</t>
+          <t>724391</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4116,32 +4116,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1102302</t>
+          <t>1229002</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1081532</t>
+          <t>1209294</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1120747</t>
+          <t>1247257</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>89,25%</t>
         </is>
       </c>
     </row>
@@ -4159,17 +4159,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>513077</t>
+          <t>576601</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>513077</t>
+          <t>576601</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>513077</t>
+          <t>576601</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4194,17 +4194,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>752735</t>
+          <t>820857</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>752735</t>
+          <t>820857</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>752735</t>
+          <t>820857</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4229,17 +4229,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1265812</t>
+          <t>1397458</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1265812</t>
+          <t>1397458</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1265812</t>
+          <t>1397458</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37728</t>
+          <t>40020</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25633</t>
+          <t>30020</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50427</t>
+          <t>51946</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37670</t>
+          <t>40594</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26349</t>
+          <t>31903</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48100</t>
+          <t>51202</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>75398</t>
+          <t>80614</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>59883</t>
+          <t>66897</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>97473</t>
+          <t>95595</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -4389,32 +4389,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2250522</t>
+          <t>2188323</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2176397</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2262617</t>
+          <t>2198323</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4424,32 +4424,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2198806</t>
+          <t>2129462</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2188376</t>
+          <t>2118854</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2210127</t>
+          <t>2138153</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4459,32 +4459,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4449328</t>
+          <t>4317785</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4427253</t>
+          <t>4302804</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4464843</t>
+          <t>4331502</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -4502,17 +4502,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2288250</t>
+          <t>2228343</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2288250</t>
+          <t>2228343</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2288250</t>
+          <t>2228343</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4537,17 +4537,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2236476</t>
+          <t>2170056</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2236476</t>
+          <t>2170056</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2236476</t>
+          <t>2170056</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4572,17 +4572,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4524726</t>
+          <t>4398399</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4524726</t>
+          <t>4398399</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4524726</t>
+          <t>4398399</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4619,32 +4619,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10252</t>
+          <t>10551</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>6288</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16284</t>
+          <t>17636</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4654,32 +4654,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>13076</t>
+          <t>15425</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8213</t>
+          <t>9826</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22818</t>
+          <t>24644</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4689,27 +4689,27 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>23328</t>
+          <t>25976</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16344</t>
+          <t>18603</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33190</t>
+          <t>36703</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4732,32 +4732,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>635669</t>
+          <t>700168</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>629637</t>
+          <t>693083</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>639958</t>
+          <t>704431</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4767,32 +4767,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>646109</t>
+          <t>718039</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>636367</t>
+          <t>708820</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>650972</t>
+          <t>723638</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4802,22 +4802,22 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1281778</t>
+          <t>1418207</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1271916</t>
+          <t>1407480</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1288762</t>
+          <t>1425580</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -4845,17 +4845,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>645921</t>
+          <t>710719</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>645921</t>
+          <t>710719</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>645921</t>
+          <t>710719</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4880,17 +4880,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>659185</t>
+          <t>733464</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>659185</t>
+          <t>733464</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>659185</t>
+          <t>733464</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4915,17 +4915,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1305106</t>
+          <t>1444183</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1305106</t>
+          <t>1444183</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1305106</t>
+          <t>1444183</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4962,32 +4962,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>105444</t>
+          <t>109619</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80658</t>
+          <t>94401</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>126433</t>
+          <t>127090</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4997,32 +4997,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>156792</t>
+          <t>165427</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>130615</t>
+          <t>146195</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>182851</t>
+          <t>186297</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5032,32 +5032,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>262236</t>
+          <t>275046</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>223484</t>
+          <t>248700</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>295663</t>
+          <t>300790</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -5075,32 +5075,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3341804</t>
+          <t>3406043</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3320815</t>
+          <t>3388572</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3366590</t>
+          <t>3421261</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5110,32 +5110,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3491604</t>
+          <t>3558951</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3465545</t>
+          <t>3538081</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3517781</t>
+          <t>3578183</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5145,32 +5145,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6833408</t>
+          <t>6964994</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6799981</t>
+          <t>6939250</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6872160</t>
+          <t>6991340</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,56%</t>
         </is>
       </c>
     </row>
@@ -5188,17 +5188,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3447248</t>
+          <t>3515662</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3447248</t>
+          <t>3515662</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3447248</t>
+          <t>3515662</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5223,17 +5223,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3648396</t>
+          <t>3724378</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3648396</t>
+          <t>3724378</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3648396</t>
+          <t>3724378</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5258,17 +5258,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7095644</t>
+          <t>7240040</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7095644</t>
+          <t>7240040</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7095644</t>
+          <t>7240040</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
